--- a/data/Lüterkofen-Ichertswil/cost/cost_report.xlsx
+++ b/data/Lüterkofen-Ichertswil/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>186.4149862279542</v>
+        <v>163.6720869250634</v>
       </c>
       <c r="C2" t="n">
-        <v>4996.354570803145</v>
+        <v>5046.237801302192</v>
       </c>
       <c r="D2" t="n">
-        <v>-2697.038879686841</v>
+        <v>-2279.900448870867</v>
       </c>
       <c r="E2" t="n">
-        <v>1332.956095512159</v>
+        <v>1133.175251909039</v>
       </c>
       <c r="F2" t="n">
-        <v>14543.6003662489</v>
+        <v>14181.44553072647</v>
       </c>
       <c r="G2" t="n">
-        <v>18362.28713910531</v>
+        <v>18244.63022199189</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.119953090759279</v>
+        <v>2.860427703772039</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>187.5268508243313</v>
+        <v>164.3224987872127</v>
       </c>
       <c r="C3" t="n">
-        <v>4989.187422439662</v>
+        <v>4976.905905490506</v>
       </c>
       <c r="D3" t="n">
-        <v>-2430.151448601336</v>
+        <v>-1636.043663486718</v>
       </c>
       <c r="E3" t="n">
-        <v>1290.137484767283</v>
+        <v>1001.586472025089</v>
       </c>
       <c r="F3" t="n">
-        <v>14906.42606900381</v>
+        <v>14309.0399589074</v>
       </c>
       <c r="G3" t="n">
-        <v>18943.12637843375</v>
+        <v>18815.81117172349</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1237474689575881</v>
+        <v>2.949978535583894</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>187.6633173761092</v>
+        <v>166.6134560236976</v>
       </c>
       <c r="C4" t="n">
-        <v>2341.931209150021</v>
+        <v>2380.07694691991</v>
       </c>
       <c r="D4" t="n">
-        <v>10939.23846198751</v>
+        <v>11921.98499389764</v>
       </c>
       <c r="E4" t="n">
-        <v>921.4044412213868</v>
+        <v>647.4833169246588</v>
       </c>
       <c r="F4" t="n">
-        <v>9223.601253407947</v>
+        <v>7657.414623429195</v>
       </c>
       <c r="G4" t="n">
-        <v>23613.83868314297</v>
+        <v>22773.5733371951</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1542592659223624</v>
+        <v>3.57048398871222</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>187.5801159797768</v>
+        <v>166.6559749474428</v>
       </c>
       <c r="C5" t="n">
-        <v>2323.898569189276</v>
+        <v>2397.387146318317</v>
       </c>
       <c r="D5" t="n">
-        <v>10766.87137717965</v>
+        <v>12030.0905960736</v>
       </c>
       <c r="E5" t="n">
-        <v>1000.598050455299</v>
+        <v>650.2870047451289</v>
       </c>
       <c r="F5" t="n">
-        <v>8682.754716313291</v>
+        <v>8157.575414890297</v>
       </c>
       <c r="G5" t="n">
-        <v>22961.70282911729</v>
+        <v>23401.99613697478</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1499991369584313</v>
+        <v>3.66900930626045</v>
       </c>
     </row>
   </sheetData>
